--- a/PicoTracker.xlsx
+++ b/PicoTracker.xlsx
@@ -8,38 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidthrower/Documents/My Documents/Claude Context/Pico Balloons/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3447262C-ED67-5C4A-9867-477989A3A331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{456204C8-6978-2D44-85D5-3C8045FE45DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{AC0FE225-CCFC-D743-8320-D8E3A4A16BC9}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Flight Paths" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
   <si>
     <t>PICO Balloon Tracker</t>
   </si>
@@ -50,6 +32,24 @@
     <t>Launch</t>
   </si>
   <si>
+    <t>Lost Signal</t>
+  </si>
+  <si>
+    <t>Miles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of </t>
+  </si>
+  <si>
+    <t>Number of</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -59,9 +59,18 @@
     <t>Transmitter</t>
   </si>
   <si>
+    <t>Band</t>
+  </si>
+  <si>
     <t>Balloon</t>
   </si>
   <si>
+    <t>Stretched</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
     <t>Antenna</t>
   </si>
   <si>
@@ -71,74 +80,86 @@
     <t>Other</t>
   </si>
   <si>
-    <t>Lost Signal</t>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Traveled</t>
+  </si>
+  <si>
+    <t>World Circum.</t>
+  </si>
+  <si>
+    <t>Days aloft</t>
+  </si>
+  <si>
+    <t>Altitude</t>
   </si>
   <si>
     <t>Comments</t>
   </si>
   <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>Gas</t>
+    <t>Live Map</t>
+  </si>
+  <si>
+    <t>Traquito Jetpack</t>
+  </si>
+  <si>
+    <t>20M</t>
   </si>
   <si>
     <t>H2</t>
   </si>
   <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Miles</t>
-  </si>
-  <si>
-    <t>Traveled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of </t>
-  </si>
-  <si>
-    <t>World Circum.</t>
-  </si>
-  <si>
-    <t>Band</t>
-  </si>
-  <si>
-    <t>20M</t>
-  </si>
-  <si>
     <t>4325mm</t>
   </si>
   <si>
-    <t>Traquito Jetpack</t>
-  </si>
-  <si>
     <t>Solar System</t>
   </si>
   <si>
+    <t>View Live →</t>
+  </si>
+  <si>
     <t>PowerFilm</t>
   </si>
   <si>
-    <t>Stretched</t>
-  </si>
-  <si>
-    <t>Number of</t>
-  </si>
-  <si>
-    <t>Days aloft</t>
-  </si>
-  <si>
-    <t>General</t>
-  </si>
-  <si>
-    <t>Altitude</t>
+    <t>(assign channel)</t>
+  </si>
+  <si>
+    <t>PICO Balloon Tracker — Flight Paths</t>
+  </si>
+  <si>
+    <t>Paste each path screenshot in the Path column (Insert ▸ Pictures ▸ Place in Cell). Live Map opens the interactive Traquito map.</t>
+  </si>
+  <si>
+    <t>Flight</t>
+  </si>
+  <si>
+    <t>Launch Date</t>
+  </si>
+  <si>
+    <t>Path Screenshot</t>
+  </si>
+  <si>
+    <t>Flight 1</t>
+  </si>
+  <si>
+    <t>Flight 2</t>
+  </si>
+  <si>
+    <t>Flight 3</t>
+  </si>
+  <si>
+    <t>Flight 4</t>
+  </si>
+  <si>
+    <t>Flight 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -161,10 +182,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="12"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF808080"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="2">
@@ -187,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -206,6 +252,23 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -540,12 +603,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C8A9DBE-8064-8E40-B5D4-7A6E20D8996B}">
-  <dimension ref="A1:R13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="5"/>
+    <col min="2" max="2" width="10.83203125" style="5" customWidth="1"/>
     <col min="3" max="3" width="12" style="6" customWidth="1"/>
     <col min="4" max="4" width="14.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.1640625" style="5" customWidth="1"/>
@@ -554,241 +617,368 @@
     <col min="10" max="10" width="14" style="5" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="5" customWidth="1"/>
     <col min="12" max="12" width="35.33203125" customWidth="1"/>
-    <col min="13" max="14" width="10.83203125" style="4"/>
+    <col min="13" max="14" width="10.83203125" style="4" customWidth="1"/>
     <col min="15" max="15" width="13" style="4" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="13" style="4" customWidth="1"/>
     <col min="18" max="18" width="84" style="4" customWidth="1"/>
+    <col min="19" max="19" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="19" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="19" customHeight="1">
       <c r="A2" s="2">
         <v>46203</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" s="7" customFormat="1">
       <c r="B6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="L6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" s="7" customFormat="1">
+      <c r="A7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="N6" s="8" t="s">
+      <c r="D7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="J7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="P6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="L7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="O7" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" s="5">
         <v>1</v>
       </c>
       <c r="B8" s="6"/>
-      <c r="C8" s="5"/>
+      <c r="C8" s="5">
+        <v>290</v>
+      </c>
       <c r="D8" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8"/>
+        <v>30</v>
+      </c>
       <c r="L8" s="4"/>
-      <c r="R8"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" s="5">
         <v>2</v>
       </c>
       <c r="B9" s="6"/>
-      <c r="C9" s="5"/>
+      <c r="C9" s="5">
+        <v>291</v>
+      </c>
       <c r="D9" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9"/>
+        <v>30</v>
+      </c>
       <c r="L9" s="4"/>
-      <c r="R9"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" s="5">
         <v>3</v>
       </c>
       <c r="B10" s="6"/>
-      <c r="C10" s="5"/>
+      <c r="C10" s="5">
+        <v>292</v>
+      </c>
       <c r="D10" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10"/>
+        <v>30</v>
+      </c>
       <c r="L10" s="4"/>
-      <c r="R10"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" s="5">
         <v>4</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11"/>
+        <v>32</v>
+      </c>
       <c r="L11" s="4"/>
-      <c r="R11"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" s="5">
         <v>5</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12"/>
+        <v>32</v>
+      </c>
       <c r="L12" s="4"/>
-      <c r="R12"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="5"/>
-      <c r="K13"/>
       <c r="L13" s="4"/>
-      <c r="R13"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="S8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="S10" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="19">
+      <c r="A1" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="150" customHeight="1">
+      <c r="A5" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="14">
+        <v>290</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="15"/>
+    </row>
+    <row r="6" spans="1:5" ht="150" customHeight="1">
+      <c r="A6" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="14">
+        <v>291</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="15"/>
+    </row>
+    <row r="7" spans="1:5" ht="150" customHeight="1">
+      <c r="A7" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="14">
+        <v>292</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="15"/>
+    </row>
+    <row r="8" spans="1:5" ht="150" customHeight="1">
+      <c r="A8" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="15"/>
+    </row>
+    <row r="9" spans="1:5" ht="150" customHeight="1">
+      <c r="A9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="15"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D5" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="D6" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="D7" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>